--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_62645.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_62645.xlsx
@@ -545,7 +545,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ppc</t>
+          <t>Klple juzllelylj</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>LSUALULELL</t>
         </is>
       </c>
     </row>
